--- a/data/trans_orig/IMC_Medido-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IMC_Medido-Habitat-trans_orig.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Índice de masa corporal (IMC) medio de los menores medido</t>
+          <t>Índice de masa corporal (IMC) medio de los menores medido (tasa de respuesta: 78,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>19,07; 21,27</t>
+          <t>19,1; 21,27</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>18,45; 19,52</t>
+          <t>18,4; 19,48</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17,97; 19,98</t>
+          <t>17,93; 19,97</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19,45; 20,82</t>
+          <t>19,46; 20,76</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>18,86; 20,41</t>
+          <t>18,84; 20,36</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,79; 20,63</t>
+          <t>18,74; 20,51</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,44; 20,61</t>
+          <t>19,45; 20,61</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>18,8; 19,83</t>
+          <t>18,85; 19,82</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>18,67; 20,01</t>
+          <t>18,72; 20,09</t>
         </is>
       </c>
     </row>
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>18,45; 19,39</t>
+          <t>18,48; 19,4</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>18,07; 18,9</t>
+          <t>18,06; 18,92</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18,07; 20,07</t>
+          <t>18,12; 20,04</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19,39; 20,55</t>
+          <t>19,4; 20,49</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>18,42; 19,29</t>
+          <t>18,41; 19,27</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,31; 21,12</t>
+          <t>19,36; 21,06</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,07; 19,81</t>
+          <t>19,1; 19,86</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>18,36; 19,0</t>
+          <t>18,36; 18,99</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>19,04; 20,42</t>
+          <t>19,13; 20,31</t>
         </is>
       </c>
     </row>
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>19,1; 20,53</t>
+          <t>19,09; 20,59</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18,01; 19,04</t>
+          <t>18,03; 19,03</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18,8; 22,34</t>
+          <t>18,71; 22,37</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18,85; 20,06</t>
+          <t>18,89; 20,11</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>17,69; 18,68</t>
+          <t>17,66; 18,64</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18,19; 19,9</t>
+          <t>18,23; 20,02</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19,18; 20,08</t>
+          <t>19,14; 20,1</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>17,99; 18,69</t>
+          <t>17,94; 18,65</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>18,76; 21,52</t>
+          <t>18,79; 21,21</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>19,07; 20,31</t>
+          <t>19,09; 20,35</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>18,69; 20,07</t>
+          <t>18,68; 20,06</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18,41; 20,8</t>
+          <t>18,42; 20,77</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19,15; 20,26</t>
+          <t>19,13; 20,26</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>18,82; 20,15</t>
+          <t>18,86; 20,09</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,17; 19,86</t>
+          <t>18,22; 19,88</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,28; 20,1</t>
+          <t>19,25; 20,08</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>18,91; 19,84</t>
+          <t>18,91; 19,82</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>18,54; 20,03</t>
+          <t>18,54; 20,04</t>
         </is>
       </c>
     </row>
@@ -1117,32 +1117,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>19,19; 19,89</t>
+          <t>19,18; 19,83</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>18,52; 19,07</t>
+          <t>18,5; 19,04</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18,84; 20,67</t>
+          <t>18,79; 20,64</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19,48; 20,09</t>
+          <t>19,45; 20,08</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>18,68; 19,31</t>
+          <t>18,72; 19,26</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,06; 19,96</t>
+          <t>19,09; 19,96</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1152,12 +1152,12 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>18,68; 19,08</t>
+          <t>18,68; 19,09</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>19,11; 20,09</t>
+          <t>19,08; 20,13</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IMC_Medido-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IMC_Medido-Habitat-trans_orig.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Índice de masa corporal (IMC) medio de los menores medido (tasa de respuesta: 78,69%)</t>
+          <t>Índice de masa corporal (IMC) medio de los menores, recogido por medición (tasa de respuesta: 78,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>19,1; 21,27</t>
+          <t>19,06; 21,03</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>18,4; 19,48</t>
+          <t>18,42; 19,42</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17,93; 19,97</t>
+          <t>17,92; 19,97</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19,46; 20,76</t>
+          <t>19,37; 20,77</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>18,84; 20,36</t>
+          <t>18,83; 20,36</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,74; 20,51</t>
+          <t>18,8; 20,58</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,45; 20,61</t>
+          <t>19,44; 20,61</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>18,85; 19,82</t>
+          <t>18,81; 19,73</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>18,72; 20,09</t>
+          <t>18,64; 20,05</t>
         </is>
       </c>
     </row>
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>18,48; 19,4</t>
+          <t>18,5; 19,42</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>18,06; 18,92</t>
+          <t>18,03; 18,94</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18,12; 20,04</t>
+          <t>18,16; 20,2</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19,4; 20,49</t>
+          <t>19,4; 20,56</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>18,41; 19,27</t>
+          <t>18,38; 19,3</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,36; 21,06</t>
+          <t>19,28; 21,03</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,1; 19,86</t>
+          <t>19,09; 19,85</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>18,36; 18,99</t>
+          <t>18,32; 19,0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>19,13; 20,31</t>
+          <t>19,07; 20,42</t>
         </is>
       </c>
     </row>
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>19,09; 20,59</t>
+          <t>19,09; 20,54</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18,03; 19,03</t>
+          <t>17,98; 19,01</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18,71; 22,37</t>
+          <t>18,68; 22,37</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18,89; 20,11</t>
+          <t>18,92; 20,09</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>17,66; 18,64</t>
+          <t>17,64; 18,63</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18,23; 20,02</t>
+          <t>18,21; 19,9</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19,14; 20,1</t>
+          <t>19,14; 20,14</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>17,94; 18,65</t>
+          <t>17,94; 18,64</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>18,79; 21,21</t>
+          <t>18,74; 21,38</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>19,09; 20,35</t>
+          <t>19,07; 20,4</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>18,68; 20,06</t>
+          <t>18,66; 20,02</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18,42; 20,77</t>
+          <t>18,36; 21,1</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19,13; 20,26</t>
+          <t>19,11; 20,28</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>18,86; 20,09</t>
+          <t>18,85; 20,12</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,22; 19,88</t>
+          <t>18,23; 19,96</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,25; 20,08</t>
+          <t>19,26; 20,1</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>18,91; 19,82</t>
+          <t>18,93; 19,87</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>18,54; 20,04</t>
+          <t>18,5; 20,04</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1117,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>19,18; 19,83</t>
+          <t>19,17; 19,86</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>18,5; 19,04</t>
+          <t>18,5; 19,06</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18,79; 20,64</t>
+          <t>18,79; 20,66</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19,45; 20,08</t>
+          <t>19,44; 20,08</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>18,72; 19,26</t>
+          <t>18,7; 19,31</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,09; 19,96</t>
+          <t>19,07; 20,01</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,42; 19,89</t>
+          <t>19,44; 19,87</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>18,68; 19,09</t>
+          <t>18,68; 19,08</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>19,08; 20,13</t>
+          <t>19,1; 20,12</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IMC_Medido-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IMC_Medido-Habitat-trans_orig.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>20,07</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>19,56</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>19,87</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>19,82</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>18,91</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>18,85</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>20,07</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>19,56</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,69</t>
+          <t>18,81</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>19,35</t>
+          <t>19,42</t>
         </is>
       </c>
     </row>
@@ -677,32 +677,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>19,06; 21,03</t>
+          <t>19,45; 20,82</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>18,42; 19,42</t>
+          <t>18,86; 20,41</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17,92; 19,97</t>
+          <t>19,02; 20,89</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19,37; 20,77</t>
+          <t>19,07; 21,27</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>18,83; 20,36</t>
+          <t>18,45; 19,52</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,8; 20,58</t>
+          <t>17,89; 19,97</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -712,12 +712,12 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>18,81; 19,73</t>
+          <t>18,8; 19,83</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>18,64; 20,05</t>
+          <t>18,77; 20,09</t>
         </is>
       </c>
     </row>
@@ -734,32 +734,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>19,9</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>18,84</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>20,24</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>18,94</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>18,46</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>18,9</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>19,9</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>18,84</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>20,11</t>
+          <t>19,02</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>19,65</t>
+          <t>19,76</t>
         </is>
       </c>
     </row>
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>18,5; 19,42</t>
+          <t>19,39; 20,55</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>18,03; 18,94</t>
+          <t>18,42; 19,29</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18,16; 20,2</t>
+          <t>19,41; 21,25</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19,4; 20,56</t>
+          <t>18,45; 19,39</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>18,38; 19,3</t>
+          <t>18,07; 18,9</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,28; 21,03</t>
+          <t>18,19; 20,2</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,09; 19,85</t>
+          <t>19,07; 19,81</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>18,32; 19,0</t>
+          <t>18,36; 19,0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>19,07; 20,42</t>
+          <t>19,16; 20,54</t>
         </is>
       </c>
     </row>
@@ -844,32 +844,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>19,48</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>18,15</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>19,06</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>19,76</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>18,49</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>20,41</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>19,48</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>18,15</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>18,96</t>
+          <t>19,17</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>19,72</t>
+          <t>19,11</t>
         </is>
       </c>
     </row>
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>19,09; 20,54</t>
+          <t>18,85; 20,06</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17,98; 19,01</t>
+          <t>17,69; 18,68</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18,68; 22,37</t>
+          <t>18,28; 20,02</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18,92; 20,09</t>
+          <t>19,1; 20,53</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>17,64; 18,63</t>
+          <t>18,01; 19,04</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18,21; 19,9</t>
+          <t>18,29; 20,45</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19,14; 20,14</t>
+          <t>19,18; 20,08</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>17,94; 18,64</t>
+          <t>17,99; 18,69</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>18,74; 21,38</t>
+          <t>18,51; 19,85</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>19,66</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>19,4</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>18,98</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>19,67</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>19,23</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>19,3</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>19,66</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>19,4</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,92</t>
+          <t>19,05</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>19,11</t>
+          <t>19,01</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>19,07; 20,4</t>
+          <t>19,15; 20,26</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>18,66; 20,02</t>
+          <t>18,82; 20,15</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18,36; 21,1</t>
+          <t>18,23; 19,92</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19,11; 20,28</t>
+          <t>19,07; 20,31</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>18,85; 20,12</t>
+          <t>18,69; 20,07</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,23; 19,96</t>
+          <t>18,33; 20,21</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,26; 20,1</t>
+          <t>19,28; 20,1</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>18,93; 19,87</t>
+          <t>18,91; 19,84</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>18,5; 20,04</t>
+          <t>18,5; 19,65</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>19,78</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>18,98</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>19,61</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>19,5</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>18,77</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>19,47</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>19,78</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>18,98</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>19,49</t>
+          <t>19,03</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>19,48</t>
+          <t>19,35</t>
         </is>
       </c>
     </row>
@@ -1117,37 +1117,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>19,17; 19,86</t>
+          <t>19,48; 20,09</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>18,5; 19,06</t>
+          <t>18,68; 19,31</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18,79; 20,66</t>
+          <t>19,19; 20,09</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19,44; 20,08</t>
+          <t>19,19; 19,89</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>18,7; 19,31</t>
+          <t>18,52; 19,07</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,07; 20,01</t>
+          <t>18,6; 19,61</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,44; 19,87</t>
+          <t>19,42; 19,89</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1157,7 +1157,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>19,1; 20,12</t>
+          <t>19,02; 19,69</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IMC_Medido-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IMC_Medido-Habitat-trans_orig.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +140,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -523,7 +528,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Índice de masa corporal (IMC) medio de los menores, recogido por medición (tasa de respuesta: 78,69%)</t>
+          <t>Índice de masa corporal (IMC) medio de los menores, recogido por medición (tasa de respuesta: 81,88%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -622,329 +627,217 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>20,07</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>19,56</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>19,87</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>19,82</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>18,91</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>18,81</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>19,95</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>19,26</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>19,42</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>20.06737451614642</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>19.56496795356507</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>19.87253728400032</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>19.81623273023817</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>18.90648201797542</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>18.80665672730251</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>19.94521212386582</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>19.25549411622453</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>19.41784460492461</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>19,45; 20,82</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>18,86; 20,41</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>19,02; 20,89</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>19,07; 21,27</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>18,45; 19,52</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>17,89; 19,97</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>19,44; 20,61</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>18,8; 19,83</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>18,77; 20,09</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>19.45060025995399</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>18.85902786164905</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>19.01951174196584</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>19.07399091370912</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>18.44840185735727</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>17.88721575369952</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>19.43830517981668</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>18.80434129705963</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>18.76695846711597</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>20.8160827226617</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>20.40642579596008</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>20.88818696193076</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>21.26812876958344</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>19.51678789089134</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>19.96755305011034</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>20.61084120472358</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>19.82981175406748</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>20.09272684385052</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>10-50.000 hab</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>19,9</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>18,84</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>20,24</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>18,94</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>18,46</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>19,02</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>19,44</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>18,66</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>19,76</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>19,39; 20,55</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>18,42; 19,29</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>19,41; 21,25</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>18,45; 19,39</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>18,07; 18,9</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>18,19; 20,2</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>19,07; 19,81</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>18,36; 19,0</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>19,16; 20,54</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>19.90362897009128</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>18.84195284812233</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>20.23862316705396</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>18.93999231520348</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>18.4603415036113</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>19.02036140305964</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>19.43754008221554</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>18.65757553848307</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>19.75979585146168</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>19,48</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>18,15</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>19,06</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>19,76</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>18,49</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>19,17</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>19,61</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>18,31</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>19,11</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>19.39292225689066</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>18.41759954658785</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>19.41326018387322</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>18.45262349222198</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>18.07284136433484</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>18.18792904480565</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>19.07385012814443</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>18.36499585391502</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>19.15826462081901</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>18,85; 20,06</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>17,69; 18,68</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>18,28; 20,02</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>19,1; 20,53</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>18,01; 19,04</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>18,29; 20,45</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>19,18; 20,08</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>17,99; 18,69</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>18,51; 19,85</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>20.55139189938372</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>19.28853762379528</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>21.25006208382148</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>19.38776442047857</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>18.90039909745065</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>20.19724427302498</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>19.80551757994461</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>18.99891266997613</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>20.54399734409108</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Capitales</t>
+          <t>&gt;50.000 hab</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -952,217 +845,324 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>19,66</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>19,4</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>18,98</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>19,67</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>19,23</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>19,05</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>19,67</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>19,32</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>19,01</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>19.47769889547275</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>18.14528586221614</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>19.05832076380279</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>19.75821144630212</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>18.48640372665188</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>19.17229691566229</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>19.61423717739228</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>18.30733796643916</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>19.109699851284</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>19,15; 20,26</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>18,82; 20,15</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>18,23; 19,92</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>19,07; 20,31</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>18,69; 20,07</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>18,33; 20,21</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>19,28; 20,1</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>18,91; 19,84</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>18,5; 19,65</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>18.84741339711126</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>17.69428949039522</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>18.27683599627189</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>19.09675483674369</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>18.0149743105863</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>18.29272941260449</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>19.17562230453933</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>17.99051735044211</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>18.51241367052952</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>20.06017365177507</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>18.67741593256547</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>20.02496244222496</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>20.53350350721655</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>19.04051703801821</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>20.45215595873563</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>20.07658685165948</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>18.69185554062776</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>19.84956498403681</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>19.66251026271422</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>19.40032823367305</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>18.98153604417481</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>19.67091312213918</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>19.23425855571843</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>19.04621441705725</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>19.66666403693428</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>19.32073899046743</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>19.01486325397811</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>19.15453793972197</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>18.82486337643853</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>18.23010269297259</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>19.07009679042007</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>18.69359896668551</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>18.32799934471847</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>19.2793277113298</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>18.91113337446892</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>18.50428185751068</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>20.25845635826301</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>20.14944429468653</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>19.91719218102203</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>20.30548420622922</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>20.06835920165483</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>20.21420056168946</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>20.10205202719724</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>19.8384180157963</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>19.65492965772765</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>19,78</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>18,98</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>19,61</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>19,5</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>18,77</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>19,03</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>19,64</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>18,88</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>19,35</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>19,48; 20,09</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>18,68; 19,31</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>19,19; 20,09</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>19,19; 19,89</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>18,52; 19,07</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>18,6; 19,61</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>19,42; 19,89</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>18,68; 19,08</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>19,02; 19,69</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>19.77734618549</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>18.97777263197639</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>19.60638206017093</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>19.50069028820386</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>18.77159943671817</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>19.02635636669282</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>19.64237760674442</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>18.87929111441086</v>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>19.34818702368086</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>19.48127154246051</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>18.68351430363325</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>19.18738829380854</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>19.18925687107792</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>18.52246053296223</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>18.59656079178614</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>19.42259206053732</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>18.67598961102727</v>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>19.01897153474659</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>20.08600514812158</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>19.31294092105166</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>20.08517271000238</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>19.88627677988524</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>19.06876213998896</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>19.61027127031906</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>19.89025559794597</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>19.07831773694881</v>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>19.68628245385836</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1171,14 +1171,14 @@
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="I1:K1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/trans_orig/IMC_Medido-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IMC_Medido-Habitat-trans_orig.xlsx
@@ -528,7 +528,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Índice de masa corporal (IMC) medio de los menores, recogido por medición (tasa de respuesta: 81,88%)</t>
+          <t>Índice de masa corporal (IMC) medio de los menores, recogido por medición (tasa de respuesta: 78,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
